--- a/StructureDefinition-insulin-on-hyperglycemia-medication-administration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medication-administration-profile.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T10:11:46+00:00</t>
+    <t>2026-09-23T10:52:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-insulin-on-hyperglycemia-medication-administration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:36+00:00</t>
+    <t>2026-09-23T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-insulin-on-hyperglycemia-medication-administration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medication-administration-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2131" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2131" uniqueCount="416">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:57+00:00</t>
+    <t>2026-10-14T14:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1270,6 +1270,10 @@
   </si>
   <si>
     <t>If the administration is not instantaneous (rate is present), this can be specified to convey the total amount administered over period of time of a single administration.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>.doseQuantity</t>
@@ -8100,7 +8104,7 @@
         <v>370</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>77</v>
@@ -8109,18 +8113,18 @@
         <v>77</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8143,16 +8147,16 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8202,7 +8206,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8223,18 +8227,18 @@
         <v>77</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8257,16 +8261,16 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8316,7 +8320,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8337,7 +8341,7 @@
         <v>77</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>77</v>

--- a/StructureDefinition-insulin-on-hyperglycemia-medication-administration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T14:44:50+00:00</t>
+    <t>2026-10-15T10:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-insulin-on-hyperglycemia-medication-administration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:29:33+00:00</t>
+    <t>2026-10-19T07:01:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-insulin-on-hyperglycemia-medication-administration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T07:01:38+00:00</t>
+    <t>2026-10-28T15:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
